--- a/practice-files/day05-数据验证与条件格式.xlsx
+++ b/practice-files/day05-数据验证与条件格式.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="练习说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品定价" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品定价" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -579,19 +578,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/practice-files/day05-数据验证与条件格式.xlsx
+++ b/practice-files/day05-数据验证与条件格式.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -494,74 +494,88 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1. 选中"分类"列→数据→数据验证→序列→来源输入"电子产品,服装鞋帽,食品饮料,家居用品,运动户外"</t>
+          <t>WPS提示：WPS里这个功能叫"有效性"（或数据有效性），位置一样在"数据"选项卡，找不到就用顶部搜索框搜"有效性"</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → 现在分类列只能从下拉列表里选，不能随便打字了</t>
+          <t>1. 选中"分类"列→数据→数据验证/有效性→序列→来源输入"电子产品,服装鞋帽,食品饮料,家居用品,运动户外"（英文逗号）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2. 选中"价格"列→数据验证→小数→介于13到3000→防止输入异常价格</t>
+          <t xml:space="preserve">   → 现在分类列只能从下拉列表里选，不能随便打字了</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>3. 选中"库存"列→数据验证→整数→介于0到9999</t>
+          <t>2. 选中"价格"列→数据验证/有效性→小数→介于13到3000→防止输入异常价格</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>3. 选中"库存"列→数据验证/有效性→整数→介于0到9999</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>【条件格式】</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1. 选中价格列→开始→条件格式→突出显示→大于→1000→设为红色</t>
+          <t>【条件格式】</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2. 再加一条：小于100→设为绿色</t>
+          <t>WPS提示：WPS里也叫"条件格式"，位置一样在"开始"选项卡，数据条/色阶/图标集都有</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>3. 选中库存列→条件格式→数据条→一眼看出库存高低</t>
+          <t>1. 选中价格列→开始→条件格式→突出显示→大于→1000→设为红色</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>4. 试试色阶：选中价格列→条件格式→色阶→绿-黄-红</t>
+          <t>2. 再加一条：小于100→设为绿色</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>3. 选中库存列→条件格式→数据条→一眼看出库存高低</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>4. 试试色阶：选中价格列→条件格式→色阶→绿-黄-红</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>【思考】价格&gt;1000的和&lt;100的商品，分别是什么类型？这反映了什么定价策略？</t>
         </is>

--- a/practice-files/day05-数据验证与条件格式.xlsx
+++ b/practice-files/day05-数据验证与条件格式.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +33,22 @@
     </font>
     <font>
       <name val="微软雅黑"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00E67E22"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="002E7D32"/>
       <sz val="10.5"/>
     </font>
     <font>
@@ -86,16 +102,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -577,7 +598,56 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>【思考】价格&gt;1000的和&lt;100的商品，分别是什么类型？这反映了什么定价策略？</t>
+          <t>【思考】价格&gt;1000的和&lt;100的商品，分别是什么类型？这反映了什么定价策略？（答案见下方折叠区）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>思考题1: 数据验证和条件格式都跟"数据质量"有关，区别是什么？</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" hidden="1" outlineLevel="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>💡 答案: 数据验证是"预防"——在数据进来之前限制输入，不让错数据出现；条件格式是"体检"——数据已经存在，标出来让你看。一个管入口，一个管事后。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>思考题2: 本文件里价格&gt;1000的商品有哪些？&lt;100的又有哪些？这反映什么定价策略？</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" hidden="1" outlineLevel="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>💡 答案: &gt;1000：iPhone 15 Pro(1299)、MacBook Air(2499)、空气净化器(1999)、扫地机器人(1299)、蚕丝被(1599)——集中在电子和家居。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" hidden="1" outlineLevel="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>&lt;100：机械键盘(89)、纯棉T恤(39)、台灯LED(89)、蓝牙音箱(79)、瑜伽垫(49)——以服装和户外为主。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" hidden="1" outlineLevel="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>策略：电子/家居走高单价利润款，服装/户外走低价走量款。</t>
         </is>
       </c>
     </row>
@@ -602,474 +672,474 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>商品名称</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>分类</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>价格</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>库存</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>iPhone 15 Pro</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="7" t="n">
         <v>1299</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="7" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>AirPods Pro</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="7" t="n">
         <v>199</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="7" t="n">
         <v>230</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>MacBook Air</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="7" t="n">
         <v>2499</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="7" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>小米14</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="7" t="n">
         <v>899</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="7" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>机械键盘</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="7" t="n">
         <v>89</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="7" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>运动跑鞋</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="7" t="n">
         <v>599</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="7" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>羽绒服</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="7" t="n">
         <v>899</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="7" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>纯棉T恤</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="7" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>牛仔裤</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="7" t="n">
         <v>299</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="7" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>冲锋衣</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="7" t="n">
         <v>799</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="7" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>有机牛奶</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="7" t="n">
         <v>12.9</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="7" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>坚果礼盒</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="7" t="n">
         <v>168</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="7" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>进口红酒</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="7" t="n">
         <v>258</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="7" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>蛋白粉</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="7" t="n">
         <v>399</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="7" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>即食燕窝</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="7" t="n">
         <v>688</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="7" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>乳胶枕头</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="7" t="n">
         <v>299</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="7" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>空气净化器</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="7" t="n">
         <v>1999</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="7" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>扫地机器人</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="7" t="n">
         <v>1299</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="7" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>台灯LED</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="7" t="n">
         <v>89</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="7" t="n">
         <v>400</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>蚕丝被</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="7" t="n">
         <v>1599</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="7" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>蓝牙音箱</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="7" t="n">
         <v>79</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="7" t="n">
         <v>350</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>登山包</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="7" t="n">
         <v>459</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="7" t="n">
         <v>110</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>瑜伽垫</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="7" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>帐篷双人</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" s="7" t="n">
         <v>899</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="7" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>望远镜</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="7" t="n">
         <v>299</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="7" t="n">
         <v>85</v>
       </c>
     </row>

--- a/practice-files/day05-数据验证与条件格式.xlsx
+++ b/practice-files/day05-数据验证与条件格式.xlsx
@@ -605,7 +605,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+          <t>思考题（先自己想想，点左侧+号展开答案）</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
     <row r="23" hidden="1" outlineLevel="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>💡 答案: 数据验证是"预防"——在数据进来之前限制输入，不让错数据出现；条件格式是"体检"——数据已经存在，标出来让你看。一个管入口，一个管事后。</t>
+          <t>答案: 数据验证是"预防"——在数据进来之前限制输入，不让错数据出现；条件格式是"体检"——数据已经存在，标出来让你看。一个管入口，一个管事后。</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
     <row r="26" hidden="1" outlineLevel="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>💡 答案: &gt;1000：iPhone 15 Pro(1299)、MacBook Air(2499)、空气净化器(1999)、扫地机器人(1299)、蚕丝被(1599)——集中在电子和家居。</t>
+          <t>答案: &gt;1000：iPhone 15 Pro(1299)、MacBook Air(2499)、空气净化器(1999)、扫地机器人(1299)、蚕丝被(1599)——集中在电子和家居。</t>
         </is>
       </c>
     </row>

--- a/practice-files/day05-数据验证与条件格式.xlsx
+++ b/practice-files/day05-数据验证与条件格式.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="练习说明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品定价" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="靓号定价(备用实战)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -593,59 +594,66 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>【备用实战】"靓号定价(备用实战)"工作表模拟靓号定价表，练数据验证和条件格式用</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>【思考】价格&gt;1000的和&lt;100的商品，分别是什么类型？这反映了什么定价策略？（答案见下方折叠区）</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>思考题（先自己想想，点左侧+号展开答案）</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>思考题1: 数据验证和条件格式都跟"数据质量"有关，区别是什么？</t>
         </is>
       </c>
     </row>
-    <row r="23" hidden="1" outlineLevel="1">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24" hidden="1" outlineLevel="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>答案: 数据验证是"预防"——在数据进来之前限制输入，不让错数据出现；条件格式是"体检"——数据已经存在，标出来让你看。一个管入口，一个管事后。</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>思考题2: 本文件里价格&gt;1000的商品有哪些？&lt;100的又有哪些？这反映什么定价策略？</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" hidden="1" outlineLevel="1">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>答案: &gt;1000：iPhone 15 Pro(1299)、MacBook Air(2499)、空气净化器(1999)、扫地机器人(1299)、蚕丝被(1599)——集中在电子和家居。</t>
         </is>
       </c>
     </row>
     <row r="27" hidden="1" outlineLevel="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>&lt;100：机械键盘(89)、纯棉T恤(39)、台灯LED(89)、蓝牙音箱(79)、瑜伽垫(49)——以服装和户外为主。</t>
+          <t>答案: &gt;1000：iPhone 15 Pro(1299)、MacBook Air(2499)、空气净化器(1999)、扫地机器人(1299)、蚕丝被(1599)——集中在电子和家居。</t>
         </is>
       </c>
     </row>
     <row r="28" hidden="1" outlineLevel="1">
       <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>&lt;100：机械键盘(89)、纯棉T恤(39)、台灯LED(89)、蓝牙音箱(79)、瑜伽垫(49)——以服装和户外为主。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" hidden="1" outlineLevel="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>策略：电子/家居走高单价利润款，服装/户外走低价走量款。</t>
         </is>
@@ -1146,4 +1154,1246 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>号码</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>规律类型</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>价格(乐元)</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>上架状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>36576615</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>711116</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>88516</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>94519</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>112</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>83366</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>178</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>40244</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>293</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>612018</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>5999999</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>豹子</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>76438156</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>6900888</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>161</v>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>62888</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>0607888</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>0529888</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>64535218</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>142</v>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>2319922</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>152</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>99799552</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>5814770</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>86798</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>417</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>785555</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>豹子</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>208</v>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>71234</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>0515186</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>929911</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>816850</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>22141888</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>222927</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>73834735</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>146</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>8862392</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>198</v>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>1814124</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>37506</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>02200</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>779010</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>43410888</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>下架</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>93246</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>185188</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>179</v>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>06540515</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>5852888</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>105</v>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>30305888</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>354</v>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>056666</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>豹子</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>172</v>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>758416</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>1542222</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>豹子</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>128</v>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>6401658</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>154</v>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>下架</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>702135</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>557192</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>132</v>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>027868</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>473121</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>94</v>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>55188</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>831323</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>102</v>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>8291146</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>410</v>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>12517785</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>268018</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>844422</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>149</v>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>922995</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>145</v>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>94888</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>102</v>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>4736471</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>113</v>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>92554567</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>126</v>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>2103322</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>787747</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>506789</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>138</v>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>46600</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>116</v>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>71122</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>307</v>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/practice-files/day05-数据验证与条件格式.xlsx
+++ b/practice-files/day05-数据验证与条件格式.xlsx
@@ -1174,12 +1174,12 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>号码</t>
+          <t>靓号ID</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t>规律类型</t>
+          <t>类别</t>
         </is>
       </c>
       <c r="C1" s="6" t="inlineStr">
@@ -1189,34 +1189,34 @@
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
-          <t>上架状态</t>
+          <t>购买方式</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>36576615</t>
+          <t>55888</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C2" s="7" t="n">
-        <v>83</v>
+        <v>362</v>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>711116</t>
+          <t>118366</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
@@ -1225,18 +1225,18 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>88516</t>
+          <t>2022901</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -1245,58 +1245,58 @@
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>94519</t>
+          <t>48157788</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>AABB</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>83366</t>
+          <t>53888</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>AABB</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>直接购买</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>40244</t>
+          <t>48851606</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -1305,198 +1305,198 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>293</v>
+        <v>46</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>612018</t>
+          <t>70526666</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>豹子</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>5999999</t>
+          <t>51188</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>豹子</t>
+          <t>AABB</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>76438156</t>
+          <t>3319922</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>AABB</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>36</v>
+        <v>152</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>6900888</t>
+          <t>89955271</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>直接购买</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>62888</t>
+          <t>81111</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>豹子</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>0607888</t>
+          <t>90793597</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>70</v>
+        <v>177</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>0529888</t>
+          <t>2820377</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>64535218</t>
+          <t>6908866</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>AABB</t>
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>142</v>
+        <v>85</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>直接购买</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2319922</t>
+          <t>35462</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>AABB</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>99799552</t>
+          <t>62816850</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -1505,58 +1505,58 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>5814770</t>
+          <t>32141888</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>直接购买</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>86798</t>
+          <t>370888</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>417</v>
+        <v>376</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>785555</t>
+          <t>834444</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -1565,158 +1565,158 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>208</v>
+        <v>140</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>71234</t>
+          <t>340758</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>顺子</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>95</v>
+        <v>408</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>0515186</t>
+          <t>36666</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>豹子</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>竞拍</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>929911</t>
+          <t>95361888</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>AABB</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>竞拍</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>816850</t>
+          <t>827888</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>22141888</t>
+          <t>961434</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>222927</t>
+          <t>89808888</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>73834735</t>
+          <t>28518888</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>8862392</t>
+          <t>50515319</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -1725,18 +1725,18 @@
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>198</v>
+        <v>127</v>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>1814124</t>
+          <t>3772217</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -1745,18 +1745,18 @@
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>直接购买</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>37506</t>
+          <t>9740345</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -1765,18 +1765,18 @@
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>30</v>
+        <v>196</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>02200</t>
+          <t>7765588</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -1785,18 +1785,18 @@
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>779010</t>
+          <t>38451154</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -1805,78 +1805,78 @@
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>43410888</t>
+          <t>15965588</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>AABB</t>
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>55</v>
+        <v>154</v>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>下架</t>
+          <t>直接购买</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>93246</t>
+          <t>45888</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>185188</t>
+          <t>2924433</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>AABB</t>
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>06540515</t>
+          <t>24473947</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -1885,38 +1885,38 @@
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>5852888</t>
+          <t>815518</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>105</v>
+        <v>171</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>直接购买</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>30305888</t>
+          <t>423888</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -1925,18 +1925,18 @@
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>354</v>
+        <v>130</v>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>直接购买</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>056666</t>
+          <t>81111</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -1945,18 +1945,18 @@
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>172</v>
+        <v>22</v>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>758416</t>
+          <t>62892268</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -1965,18 +1965,18 @@
         </is>
       </c>
       <c r="C40" s="7" t="n">
-        <v>33</v>
+        <v>199</v>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>1542222</t>
+          <t>351111</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -1985,18 +1985,18 @@
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>6401658</t>
+          <t>918299</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -2005,38 +2005,38 @@
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>下架</t>
+          <t>竞拍</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>702135</t>
+          <t>53888</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>557192</t>
+          <t>5736471</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -2045,58 +2045,58 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>027868</t>
+          <t>35554567</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>顺子</t>
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>473121</t>
+          <t>20466789</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>顺子</t>
         </is>
       </c>
       <c r="C46" s="7" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>55188</t>
+          <t>977470</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -2105,118 +2105,118 @@
         </is>
       </c>
       <c r="C47" s="7" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>831323</t>
+          <t>606789</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>顺子</t>
         </is>
       </c>
       <c r="C48" s="7" t="n">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>8291146</t>
+          <t>56600</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>AABB</t>
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>410</v>
+        <v>116</v>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>12517785</t>
+          <t>81122</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>AABB</t>
         </is>
       </c>
       <c r="C50" s="7" t="n">
-        <v>42</v>
+        <v>307</v>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>268018</t>
+          <t>968888</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>844422</t>
+          <t>92595888</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>AABB</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C52" s="7" t="n">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>922995</t>
+          <t>57055169</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -2225,171 +2225,171 @@
         </is>
       </c>
       <c r="C53" s="7" t="n">
-        <v>145</v>
+        <v>94</v>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>直接购买</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>94888</t>
+          <t>4097289</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="C54" s="7" t="n">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>直接购买</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>4736471</t>
+          <t>85888</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>92554567</t>
+          <t>957865</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>顺子</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="C56" s="7" t="n">
-        <v>126</v>
+        <v>328</v>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>2103322</t>
+          <t>5973348</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>AABB</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>175</v>
+        <v>96</v>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>竞拍</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>787747</t>
+          <t>68446666</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>豹子</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
-        <v>47</v>
+        <v>176</v>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>506789</t>
+          <t>2574733</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>顺子</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>46600</t>
+          <t>4308888</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>AABB</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C60" s="7" t="n">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>926888</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>AABB</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>307</v>
+        <v>123</v>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
         </is>
       </c>
     </row>

--- a/practice-files/day05-数据验证与条件格式.xlsx
+++ b/practice-files/day05-数据验证与条件格式.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -596,64 +596,85 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>【备用实战】"靓号定价(备用实战)"工作表模拟靓号定价表，练数据验证和条件格式用</t>
+          <t>【备用实战】"靓号定价(备用实战)"工作表模拟靓号定价表（与真实后台列一致），练数据验证和条件格式用：</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. 价格列→条件格式→数据条（条越长价格越高）</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  2. 位数列→4条"等于"规则：5=红/6=橙/7=黄/8=绿（条件格式→突出显示→等于，逐条设置；色阶是渐变，给不了指定颜色）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. 靓号ID列→条件格式→突出显示→文本包含→888→自定义格式→黄色填充</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>【思考】价格&gt;1000的和&lt;100的商品，分别是什么类型？这反映了什么定价策略？（答案见下方折叠区）</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>思考题（先自己想想，点左侧+号展开答案）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>思考题1: 数据验证和条件格式都跟"数据质量"有关，区别是什么？</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" hidden="1" outlineLevel="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>答案: 数据验证是"预防"——在数据进来之前限制输入，不让错数据出现；条件格式是"体检"——数据已经存在，标出来让你看。一个管入口，一个管事后。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>思考题2: 本文件里价格&gt;1000的商品有哪些？&lt;100的又有哪些？这反映什么定价策略？</t>
+          <t>思考题1: 数据验证和条件格式都跟"数据质量"有关，区别是什么？</t>
         </is>
       </c>
     </row>
     <row r="27" hidden="1" outlineLevel="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>答案: 数据验证是"预防"——在数据进来之前限制输入，不让错数据出现；条件格式是"体检"——数据已经存在，标出来让你看。一个管入口，一个管事后。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>思考题2: 本文件里价格&gt;1000的商品有哪些？&lt;100的又有哪些？这反映什么定价策略？</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" hidden="1" outlineLevel="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
           <t>答案: &gt;1000：iPhone 15 Pro(1299)、MacBook Air(2499)、空气净化器(1999)、扫地机器人(1299)、蚕丝被(1599)——集中在电子和家居。</t>
         </is>
       </c>
     </row>
-    <row r="28" hidden="1" outlineLevel="1">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="31" hidden="1" outlineLevel="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>&lt;100：机械键盘(89)、纯棉T恤(39)、台灯LED(89)、蓝牙音箱(79)、瑜伽垫(49)——以服装和户外为主。</t>
         </is>
       </c>
     </row>
-    <row r="29" hidden="1" outlineLevel="1">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="32" hidden="1" outlineLevel="1">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>策略：电子/家居走高单价利润款，服装/户外走低价走量款。</t>
         </is>
@@ -1162,13 +1183,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1179,1217 +1202,1707 @@
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
+          <t>位数</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>价格(乐元)</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>购买方式</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>赠送VIP</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>55888</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
+          <t>53888</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>888</t>
         </is>
       </c>
-      <c r="C2" s="7" t="n">
-        <v>362</v>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+      <c r="D2" s="7" t="n">
+        <v>171</v>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>118366</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>23389888</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>156</v>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>2022901</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
+          <t>12654235</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="C4" s="7" t="n">
-        <v>82</v>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+      <c r="D4" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>48157788</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>AABB</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>104</v>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>1781618</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>VIP 1个月</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>53888</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
+          <t>44888</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>888</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>48851606</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>竞拍</t>
+          <t>5193456</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>70526666</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>豹子</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>119</v>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>130564</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>51188</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>AABB</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>142</v>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>8675678</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>121</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>3319922</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
+          <t>38716699</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>AABB</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
-        <v>152</v>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+      <c r="D10" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>89955271</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
+          <t>94514</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n">
-        <v>81</v>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>直接购买</t>
+      <c r="D11" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>VIP 1个月</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>81111</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>豹子</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>178</v>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>58932</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>90793597</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>177</v>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>64303888</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>165</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>VIP 1个月</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2820377</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+          <t>34896383</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
-        <v>149</v>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+      <c r="D14" s="7" t="n">
+        <v>132</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>6908866</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>AABB</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>85</v>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>直接购买</t>
+          <t>41509888</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>35462</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>175</v>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>151888</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>117</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>62816850</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>86313456</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>32141888</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>888</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
+          <t>23338726</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>370888</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+          <t>90888</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>888</t>
         </is>
       </c>
-      <c r="C19" s="7" t="n">
-        <v>376</v>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>竞拍</t>
+      <c r="D19" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>VIP 1个月</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>834444</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>豹子</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="n">
-        <v>140</v>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>74746888</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>340758</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+          <t>10978</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n">
-        <v>408</v>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+      <c r="D21" s="7" t="n">
+        <v>350</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>36666</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>豹子</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>竞拍</t>
+          <t>29136</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>95361888</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>888</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>竞拍</t>
+          <t>79985</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>246</v>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>827888</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
+          <t>57510888</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>888</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
-        <v>187</v>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+      <c r="D24" s="7" t="n">
+        <v>204</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>961434</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>6135888</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>156</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>89808888</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>888</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>94124</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>28518888</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>888</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="n">
-        <v>131</v>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>4530000</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>豹子</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>50515319</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="n">
-        <v>127</v>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>36688</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>3772217</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
+          <t>3620450</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="C29" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>直接购买</t>
+      <c r="D29" s="7" t="n">
+        <v>248</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>9740345</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>196</v>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
+          <t>92222</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>189</v>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>7765588</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>AABB</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>266789</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>293</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>VIP 1个月</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>38451154</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
+          <t>75414</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
-        <v>80</v>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+      <c r="D32" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>15965588</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>AABB</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="n">
-        <v>154</v>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>直接购买</t>
+          <t>52940</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>45888</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>888</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>48888</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>2924433</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>AABB</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="n">
-        <v>189</v>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>69514888</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>84</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>24473947</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>728800</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>815518</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="n">
-        <v>171</v>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
+          <t>48725511</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>160</v>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>VIP 1个月</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>423888</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
+          <t>479888</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>888</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
-        <v>130</v>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>直接购买</t>
+      <c r="D38" s="7" t="n">
+        <v>365</v>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>81111</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>豹子</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>11634567</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>62892268</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
+          <t>99579868</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
-        <v>199</v>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+      <c r="D40" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>351111</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>豹子</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="n">
-        <v>81</v>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>587347</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>918299</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
+          <t>2223623</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
-        <v>82</v>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>竞拍</t>
+      <c r="D42" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>53888</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
+          <t>76909888</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>888</t>
         </is>
       </c>
-      <c r="C43" s="7" t="n">
-        <v>140</v>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+      <c r="D43" s="7" t="n">
+        <v>276</v>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>5736471</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
+          <t>99373467</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
-        <v>113</v>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+      <c r="D44" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>VIP 1个月</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>35554567</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>顺子</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>90699016</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>20466789</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>顺子</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="n">
-        <v>78</v>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>85567777</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>豹子</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>VIP 1个月</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>977470</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
+          <t>10330</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="C47" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+      <c r="D47" s="7" t="n">
+        <v>119</v>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>606789</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>顺子</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>138</v>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>47452</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>177</v>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>56600</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>AABB</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="n">
-        <v>116</v>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>59663</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>81122</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>AABB</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="n">
-        <v>307</v>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>竞拍</t>
+          <t>59190</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>968888</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
+          <t>7716888</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>888</t>
         </is>
       </c>
-      <c r="C51" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+      <c r="D51" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>92595888</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>888</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="n">
-        <v>124</v>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>55319999</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>127</v>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>57055169</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="n">
-        <v>94</v>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>直接购买</t>
+          <t>4545888</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>141</v>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>4097289</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
+          <t>883777</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="C54" s="7" t="n">
-        <v>130</v>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>直接购买</t>
+      <c r="D54" s="7" t="n">
+        <v>107</v>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>85888</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>888</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="n">
-        <v>133</v>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>竞拍</t>
+          <t>678888</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>豹子</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>84</v>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>957865</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="n">
-        <v>328</v>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>4515678</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>5973348</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="n">
-        <v>96</v>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>竞拍</t>
+          <t>624444</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>豹子</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>68446666</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>豹子</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="n">
-        <v>176</v>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
+          <t>810947</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>2574733</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
+          <t>77190</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="C59" s="7" t="n">
-        <v>122</v>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+      <c r="D59" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>VIP 1个月</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>4308888</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>888</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>79993</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>130</v>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>926888</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>888</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="n">
-        <v>123</v>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>未售</t>
+          <t>1913341</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
